--- a/Monday_timetable.xlsx
+++ b/Monday_timetable.xlsx
@@ -603,22 +603,22 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
+          <t>ENGLISH
+(M.KHAN)</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>GEOGRAPHY
+(F.TABASSUM)</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
           <t>HISTORY
 (F.TABASSUM)</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>GEOGRAPHY
-(F.TABASSUM)</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>ENGLISH
-(M.KHAN)</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
           <t>AI
@@ -832,33 +832,33 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>HISTORY
+(F.TABASSUM)</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>BREAK</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>ENGLISH
+(Z.ZOHA)</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>MATHS
+(K.MUNEER)</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
           <t>GAMES
 (N.ABBASS)</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>BREAK</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>ENGLISH
-(Z.ZOHA)</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>MATHS
-(K.MUNEER)</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>HISTORY
-(F.TABASSUM)</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
           <t>COMPUTER
@@ -1203,8 +1203,8 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>ENGLISH
-(M.KHAN)</t>
+          <t>GAMES
+(K.KOSHILA)</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1215,596 +1215,596 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
+          <t>ENGLISH
+(M.KHAN)</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>ARABIC
+(M.SHAHID)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>8D</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>ENGLISH
+(M.KHAN)</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>URDU
+(S.AMIR)</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>GAMES
 (K.KOSHILA)</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>ARABIC
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>MATHS
+(K.MUNEER)</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>BREAK</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>SINDHI
+(M.MARVI)</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>ISLAMIAT
 (M.SHAHID)</t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>8D</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>S.ST
+(S.ANSARI)</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SCIENCE
+(F.KAMRAN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>7E</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>ENGLISH
 (M.KHAN)</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>MATHS
+(W.WASEEM)</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>COMPUTER
+(I.NAZ)</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>S.ST
+(N.AMIR)</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>BREAK</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>GENERAL SCIENCE
+(F.KAMRAN)</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>ISLAMIAT
+(A.SALAM)</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>PH
+(K.FATIMA)</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>URDU
+(H.HUMAIRA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>9A</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>BIOLOGY
+(T.TABUSSUM)</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>ISLAMIAT IX
+(S.SALMAN)</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>MATHS
+(Y.YASMEEN)</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>MATHS
+(Y.YASMEEN)</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>BREAK</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>CHEMISTRY
+(U.TYABA)</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>URDU
+(H.HUMAIRA)</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>LIBRARY
+(L.TEACHER)</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>ENGLISH
+(I.BATOOL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>9B</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>ENGLISH
+(A.NADEEM)</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>BIOLOGY
+(T.TABUSSUM)</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>ISLAMIAT IX
+(K.FATIMA)</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>MATHS
+(F.AHMED)</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>BREAK</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>MATHS
+(F.AHMED)</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>URDU
+(S.JAMEEL)</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>BIOLOGY
+(T.TABUSSUM)</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>CHEMISTRY
+(T.SABIR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>9C</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>ISLAMIAT IX
+(K.FATIMA)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>COMPUTER IX-X
+(S.SAQIBA)</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>COMPUTER IX-X
+(S.SAQIBA)</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>PHYSICS
+(F.ABBASI)</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>BREAK</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>ENGLISH
+(M.KHAN)</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>MATHS
+(R.IQBAL)</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>MATHS
+(R.IQBAL)</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>URDU
+(S.JAMEEL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>9D</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>URDU
+(H.HUMAIRA)</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>ENGLISH
+(I.BATOOL)</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>BIOLOGY
+(F.KAMRAN)</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>MATHS
+(A.ALIA)</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>BREAK</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>MATHS
+(A.ALIA)</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>ISLAMIAT IX
+(S.SALMAN)</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>PHYSICS
+(W.WASEEM)</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>PHYSICS
+(W.WASEEM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>9E</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>ENGLISH
+(Z.ZOHA)</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>CHEMISTRY
+(T.SABIR)</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>CHEMISTRY
+(T.SABIR)</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>MATHS
+(A.AHMED)</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>BREAK</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>URDU
 (S.AMIR)</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>GAMES
-(K.KOSHILA)</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>MATHS
-(K.MUNEER)</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>BREAK</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>SINDHI
-(M.MARVI)</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>ISLAMIAT
-(M.SHAHID)</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>S.ST
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>ISLAMIAT IX
+(K.FATIMA)</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>PHYSICS
+(K.HUSNAIN)</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>COMPUTER IX-X
+(K.KANWAL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>9F</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>ECONOMICS
 (S.ANSARI)</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>ENGLISH
+(Z.ZOHA)</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>GENERAL SCIENCE
-(F.KAMRAN)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>7E</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>ENGLISH
-(M.KHAN)</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>MATHS
-(W.WASEEM)</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>COMPUTER
+(U.TYABA)</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>URDU
+(S.AMIR)</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>BREAK</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>ISLAMIAT IX
+(S.SALMAN)</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>COMPUTER IX-X
 (I.NAZ)</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>S.ST
-(N.AMIR)</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>BREAK</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SCIENCE
-(F.KAMRAN)</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>ISLAMIAT
-(A.SALAM)</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>PH
-(K.FATIMA)</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>URDU
-(H.HUMAIRA)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>9A</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>MATHS
+(F.AHMED)</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>MATHS
+(F.AHMED)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>10A</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>MATHS
+(Y.YASMEEN)</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>PAKISTAN STUDIES
+(R.AMIR)</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>CHEMISTRY
+(F.IMRAN)</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>CHEMISTRY
+(F.IMRAN)</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>BREAK</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>ENGLISH
+(A.NADEEM)</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>PHYSICS
+(F.ABBASI)</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>SINDHI-X
+(R.MEMON)</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
         <is>
           <t>BIOLOGY
 (T.TABUSSUM)</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>ISLAMIAT IX
-(S.SALMAN)</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>MATHS
-(Y.YASMEEN)</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>MATHS
-(Y.YASMEEN)</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>BREAK</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>CHEMISTRY
-(U.TYABA)</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>URDU
-(H.HUMAIRA)</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>LIBRARY
-(L.TEACHER)</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>10B</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>PHYSICS
+(F.ABBASI)</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>PHYSICS
+(F.ABBASI)</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>ENGLISH
 (I.BATOOL)</t>
         </is>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>9B</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>ENGLISH
-(A.NADEEM)</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>SINDHI-X
+(G.GHAZALA)</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>BREAK</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>BIOLOGY
 (T.TABUSSUM)</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>ISLAMIAT IX
-(K.FATIMA)</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>MATHS
-(F.AHMED)</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>BREAK</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>MATHS
-(F.AHMED)</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>URDU
-(S.JAMEEL)</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>GAMES
-(K.KOSHILA)</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>CHEMISTRY
-(T.SABIR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>9C</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>ISLAMIAT IX
-(K.FATIMA)</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>COMPUTER IX-X
-(S.SAQIBA)</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>COMPUTER IX-X
-(S.SAQIBA)</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>PHYSICS
-(F.ABBASI)</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>BREAK</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>ENGLISH
-(M.KHAN)</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>MATHS
-(R.IQBAL)</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>MATHS
-(R.IQBAL)</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>URDU
-(S.JAMEEL)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>9D</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>URDU
-(H.HUMAIRA)</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>ENGLISH
-(I.BATOOL)</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>BIOLOGY
-(F.KAMRAN)</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>MATHS
-(A.ALIA)</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>BREAK</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>MATHS
-(A.ALIA)</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>ISLAMIAT IX
-(S.SALMAN)</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>PHYSICS
-(W.WASEEM)</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>PHYSICS
-(W.WASEEM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>9E</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>ENGLISH
-(Z.ZOHA)</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>CHEMISTRY
-(T.SABIR)</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>CHEMISTRY
-(T.SABIR)</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>MATHS
-(A.AHMED)</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>BREAK</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>URDU
-(S.AMIR)</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>ISLAMIAT IX
-(K.FATIMA)</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>PHYSICS
-(K.HUSNAIN)</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>COMPUTER IX-X
-(K.KANWAL)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>9F</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>ECONOMICS
-(S.ANSARI)</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>ENGLISH
-(Z.ZOHA)</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL SCIENCE
-(U.TYABA)</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>URDU
-(S.AMIR)</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>BREAK</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>ISLAMIAT IX
-(S.SALMAN)</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>COMPUTER IX-X
-(I.NAZ)</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>MATHS
-(F.AHMED)</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>MATHS
-(F.AHMED)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>10A</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>MATHS
-(Y.YASMEEN)</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>PAKISTAN STUDIES
-(R.AMIR)</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>CHEMISTRY
-(F.IMRAN)</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>CHEMISTRY
-(F.IMRAN)</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>BREAK</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>ENGLISH
-(A.NADEEM)</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>PHYSICS
-(F.ABBASI)</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>SINDHI-X
-(R.MEMON)</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>BIOLOGY
-(T.TABUSSUM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>10B</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>PHYSICS
-(F.ABBASI)</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>PHYSICS
-(F.ABBASI)</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>BIOLOGY
-(T.TABUSSUM)</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>SINDHI-X
-(G.GHAZALA)</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>BREAK</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>ENGLISH
-(I.BATOOL)</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
